--- a/tdsurvivor/Assets/Excels/EnemyConfig.xlsx
+++ b/tdsurvivor/Assets/Excels/EnemyConfig.xlsx
@@ -46,10 +46,10 @@
     <t>1001</t>
   </si>
   <si>
-    <t>Bee.Monster</t>
+    <t>monster.1001</t>
   </si>
   <si>
-    <t>Bee</t>
+    <t>Hexagon</t>
   </si>
   <si>
     <t>10</t>
@@ -356,13 +356,13 @@
   <sheetFormatPr defaultColWidth="12.57031" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.425781" customWidth="1"/>
-    <col min="2" max="2" width="13.42578" customWidth="1"/>
-    <col min="3" max="3" width="11.28516" customWidth="1"/>
+    <col min="2" max="2" width="14.42578" customWidth="1"/>
+    <col min="3" max="3" width="11.57031" customWidth="1"/>
     <col min="4" max="4" width="7.570313" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="6.855469" customWidth="1"/>
     <col min="7" max="7" width="13.57031" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="8" max="8" width="14.28516" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
